--- a/business_forms/048_it_infrastructure_audit_verification_form--business_forms.xlsx
+++ b/business_forms/048_it_infrastructure_audit_verification_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'server'}</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'server'}</t>
+          <t>server</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'network'}</t>
+          <t>network</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'database'}</t>
+          <t>database</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'storage'}</t>
+          <t>storage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'storage'}</t>
+          <t>storage</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'security'}</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'security'}</t>
+          <t>security</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'running'}</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'running'}</t>
+          <t>running</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'not_running'}</t>
+          <t>not_running</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'not_running'}</t>
+          <t>not running</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'not_installed'}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'not_installed'}</t>
+          <t>not installed</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'connected'}</t>
+          <t>connected</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'connected'}</t>
+          <t>connected</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_connected'}</t>
+          <t>not_connected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'not_connected'}</t>
+          <t>not connected</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_installed'}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'not_installed'}</t>
+          <t>not installed</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'online'}</t>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'not_configured'}</t>
+          <t>not_configured</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'not_configured'}</t>
+          <t>not configured</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'sufficient'}</t>
+          <t>sufficient</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'sufficient'}</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'insufficient'}</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'insufficient'}</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'not_configured'}</t>
+          <t>not_configured</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'not_configured'}</t>
+          <t>not configured</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'secure'}</t>
+          <t>secure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'secure'}</t>
+          <t>secure</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'not_secure'}</t>
+          <t>not_secure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'not_secure'}</t>
+          <t>not secure</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'not_configured'}</t>
+          <t>not_configured</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'not_configured'}</t>
+          <t>not configured</t>
         </is>
       </c>
     </row>
